--- a/public/downloads/factory-express-catalogue-en.xlsx
+++ b/public/downloads/factory-express-catalogue-en.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="000B5FA5"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <sz val="8"/>
     </font>
@@ -91,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -109,10 +115,13 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -480,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -513,7 +522,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Issued: 2026-07-08</t>
+          <t>Issued: 2026-07-18</t>
         </is>
       </c>
     </row>
@@ -521,6 +530,13 @@
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>The E-price is the unit price (JPY) for an order of one; discounted pricing applies to orders in units of ten. Prices and lead times are subject to change without notice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Product names link to the manufacturer's product pages on oks-germany.com.</t>
         </is>
       </c>
     </row>
@@ -617,55 +633,55 @@
 High-Performance Grease</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>MoS2-fortified grease that keeps protecting even if the oil film fails. Allows extended relubrication intervals.</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>-30 to +130
 drop pt. +195</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>2
 black
 lithium soap / mineral oil</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>350,000</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>3,600
 1.9</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>100g
 400ml
 1kg</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>900
 3,500
 6,600</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>On request
 On request
@@ -681,53 +697,53 @@
 High-Performance Grease</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>General-purpose bearing grease. Usable in a wide range of applications, allowing plants to standardise on one grease.</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>-30 to +120
 drop pt. +195</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>2
 light brown
 lithium soap / mineral oil</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>400,000</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>2,000
 1.9</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>400ml
 1kg</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>3,020
 6,800</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -742,53 +758,53 @@
 NATO spec. G-460</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Water-resistant grease with outstanding underwater rust protection. Proven in humid plants and in coastal and offshore locations exposed to seawater.</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>-25 to +80
 drop pt. +115</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>1-2
 light brown
 special calcium soap / mineral oil</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>350,000</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>5,200
 1.2</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>1kg
 400ml</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>9,500
 5,850</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>On request
 400ml</t>
@@ -802,51 +818,51 @@
 High-Performance High-Temp Grease</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>New-generation semi-synthetic grease for long-term lubrication of medium-speed, medium-load bearings. Heat resistant.</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>-30 to +150
 drop pt. &gt;+260</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>2
 light brown
 lithium complex soap / mineral oil / polyalphaolefin</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>350,000</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>2,800
 0.8</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>8,400</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -861,53 +877,53 @@
 Mox-Active*3</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Outstanding adhesion, impact-load capacity, and wear resistance from the synergy of multiple additives. Ideal for construction machinery subject to repeated impact loads.</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>-20 to +120
 drop pt. +190</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>2
 black
 MoS2 / lithium soap / mineral oil</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>250,000</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>4,200
 0.4</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>400ml
 1kg</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>4,700
 9,200</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>On request
 400ml</t>
@@ -921,52 +937,52 @@
 MoS2 Extreme-Pressure Grease</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>For low speeds, high loads, and impact loads. Extreme-pressure grease with added corrosion protection. The high-viscosity base oil keeps it in place under impact.</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>-20 to +120
 drop pt. +185</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>2
 dark grey
 MoS2 / lithium-calcium soap</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>50,000</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>1,020</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>4,800
 1.0
 @1,000 N</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>6,600</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -980,51 +996,51 @@
 High-Speed Grease</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>For high-speed rotation; also usable at polar low temperatures. For conveyors, cold stores, spindle bearings, machine tools, and control equipment.</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>-55 to +120
 drop pt. +195</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>2
 light brown
 lithium soap / ester</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>1,000,000</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>3,000
 0.4</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>20,900</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -1037,51 +1053,51 @@
 High-Temp Grease</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>No-drop-point grease that does not drip even at high temperature. Fewer regreasing cycles cut maintenance costs. Ideal for drying ovens, mixers, hot-air blowers, and rubber production.</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>-20 to +150
 no drop pt.</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>2
 black
 MoS2 / inorganic thickener / mineral oil</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>200,000</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>1,700
 0.7</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>12,200</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -1096,51 +1112,51 @@
 Mox-Active</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>High load capacity, shock absorption, adhesion, and sealing. Reduces noise. Also usable on slow, heavily loaded open gears.</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>-10 to +160
 drop pt. +240</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>1-2
 light brown
 organic thickener / mineral oil</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>300,000</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>460</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>3,200
 0.3</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>15,300</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -1154,53 +1170,53 @@
 Long-Life Grease</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>High-performance grease for versatility, long life, high loads, high temperature, high speed, and water exposure. A synthetic grease that meets every requirement to a high standard.</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>-40 to +180
 drop pt. +230</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>2
 light brown
 barium complex soap / polyalphaolefin</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>800,000</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>4,000
 0.6</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>400ml
 1kg</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>13,800
 33,600</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -1214,53 +1230,53 @@
 High-Temp Grease</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Synthetic heat- and impact-resistant grease, ideal where heat resistance and impact resistance are required at the same time.</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>-30 to +200
 drop pt. +240</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>1-2
 light brown
 organic thickener / polyalphaolefin</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>200,000</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>410</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>1,300
 2.0</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>400g
 1kg</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>12,700
 26,700</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>On request
 400ml</t>
@@ -1275,51 +1291,51 @@
 for Gears</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Long life, oxidation resistant. For high-speed, high-load gears. Semi-fluid, yet does not leak from unsealed vertical shafts.</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>-40 to +120
 drop pt. +155</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>00
 light brown
 lithium soap / polyglycol</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>600,000</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>2,000
 0.6</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>7,800</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -1335,51 +1351,51 @@
 Mox-Active</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Synthetic molybdenum grease for fans, autoclaves, drying ovens, metallurgical plants, and steelworks.</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>-10 to +180
 no drop pt.</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>2
 black
 MoS2 / inorganic thickener / polyalphaolefin</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>400,000</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>2,600
 0.7</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>On request
 400ml</t>
@@ -1395,56 +1411,56 @@
 NSF-H1*8</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Long life. Extremely high temperatures. High loads. Chemical resistant. Top-performance grease, insoluble in everything except perfluorinated solvents. Fluorine-based (PTFE/Teflon*) grease that does not drip even when ambient temperature exceeds the service range. Used mainly in precision equipment such as cameras, copiers, and printers, in drying ovens, and in food machinery. PFPE (perfluoropolyether) base oil with PTFE (polytetrafluoroethylene) thickener. CH4 compatible. (An O2-compatible grease, OKS 4225, is available as a special order.)</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>-20 to +280
 to +300 without oxygen
 no drop pt.</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>2
 white
 PTFE / organic polymer / perfluoropolyether</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>300,000</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>9,000
 0.6</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>40ml
 500g
 1kg</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>29,700
 122,000
 222,000</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>On request
 40ml</t>
@@ -1458,51 +1474,51 @@
 High-Melting-Point Grease</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Long life, oxidation resistant. Slightly firm synthetic grease.</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>-25 to +190
 drop pt. +250</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>2-3
 light brown
 aluminium complex soap / mineral oil</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>200,000</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>2,600
 0.7</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>9,500</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -1517,51 +1533,51 @@
 Mox-Active</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Synthetic high-performance lubricant with polyisobutylene. Wear resistant, rust protective, highly adhesive, penetrating. Transparent type that keeps machinery clean. Reduces noise. Lubrication and rust protection last at least two months.</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>-30 to +200
 drop pt. N/A</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>N/A
 translucent light brown
 tackifier / polyisobutylene</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>2,400
 0.4</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>1L</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>12,300</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -1577,51 +1593,51 @@
 spray can</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Synthetic high-performance lubricant with polyisobutylene. Wear resistant, rust protective, highly adhesive, penetrating. Transparent type that keeps machinery clean. Reduces noise. Lubrication and rust protection last at least two months. OKS 450 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>-30 to +200
 drop pt. N/A</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>N/A
 translucent light brown
 tackifier / polyisobutylene</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>2,400
 0.4</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>7,900</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>On request
 400ml</t>
@@ -1636,50 +1652,50 @@
 NSF-H1*8</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Highly adhesive, colourless, transparent grease that does not attack plastics or elastomers. Suitable for cleanliness-critical areas and food machinery.</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>-25 to +150
 no drop pt.</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>2
 clear
 inorganic thickener / polyalphaolefin</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>13,900</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -1693,55 +1709,55 @@
 High-Performance Grease</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>White grease that keeps lubrication points clean. Also for the textile, paper, and precision industries.</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>-30 to +120
 drop pt. +195</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>2
 white
 white solid lubricants / lithium soap / mineral oil</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>300,000</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>3,800
 0.3</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>80ml
 400ml
 1kg</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>2,440
 4,580
 9,700</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>On request
 80ml
@@ -1758,51 +1774,51 @@
 spray can</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Safe white grease that keeps lubrication points clean. Also for the textile, paper, and precision industries. OKS 470 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>-30 to +120
 drop pt. +195</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>2
 light brown
 white solid lubricants / lithium soap / mineral oil</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>300,000</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>3,800
 0.3</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>5,520</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -1815,51 +1831,51 @@
 High-Performance Grease</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Synthetic grease for high speeds and low temperatures. Also usable in filling and packaging machinery. Contains fluoropolymer (PTFE/Teflon*).</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>-50 to +140
 drop pt. +200</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>2
 light brown
 PTFE / lithium soap / polyalphaolefin</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>1,000,000</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>1,700
 1.7</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>21,900</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -1874,55 +1890,55 @@
 USDA-H1*8</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>All-round food-machinery grease with the widest range of uses in food processing, beverage filling, and pharmaceutical plants. Resists alkaline and acidic sterilising and cleaning agents.</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>-20 to +120
 drop pt. +250</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>2
 white
 aluminium complex soap / white oil</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>400,000</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>2,200
 1.8</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>400ml
 1kg
 25kg</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>6,500
 13,900
 277,500</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>On request
 On request
@@ -1938,50 +1954,50 @@
 NSF-H1*8</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Tasteless, odourless valve grease. Resists sterilising and cleaning agents.</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>-10 to +160
 no drop pt.</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>3
 light brown
 inorganic thickener / polyalphaolefin</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>1,200</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>5,340</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>On request
 80ml</t>
@@ -1997,53 +2013,53 @@
 NSF-H1*8</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Heat resistant, with long life even at high temperature. Also for parts exposed to cold or hot water and for rubber and elastomer parts. Chemically resistant — withstands alkaline and acidic sterilising and cleaning agents.</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>-25 to +160
 drop pt. +200</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>1
 light brown
 aluminium complex soap / polyalphaolefin</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>350,000</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>2,200
 0.7</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>400ml
 1kg</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>10,260
 21,400</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>On request
 On request</t>
@@ -2058,51 +2074,51 @@
 sprayable</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>For large, heavily loaded gears. Open-gear grease free of asphalt and solvents.</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>-25 to +180
 drop pt. +250</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>0-00
 black
 solid lubricants / aluminium complex soap / mineral oil</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>850</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>8,200
 N/A</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>8,100</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -2117,50 +2133,50 @@
 spray can</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Highly adhesive, with penetration that reaches fine clearances. After the solvent evaporates it forms a dry film, so it stays tack-free and does not pick up dust or sand.</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>-30 to +150
 drop pt. N/A</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>N/A
 black
 solid lubricants / natural &amp; synthetic resins / mineral oil</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>7,410</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>On request
 400ml</t>
@@ -2174,51 +2190,51 @@
 High-Adhesion Lubricant</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>For running in heavily loaded gears.</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>-25 to +180
 drop pt. +250</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>2
 black
 solid lubricants / aluminium complex soap / mineral oil</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>5,500
 N/A</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>8,800</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -2232,54 +2248,54 @@
 NSF-H1</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Highly adhesive multi-purpose silicone grease that bonds well to virtually any material. Excellent sealing, lubricity, and load capacity. No drying, softening, or oil separation across a wide temperature range. Chemically resistant — withstands acetone, ethanol, ethylene, glycol, glycerine, and methanol. The only NLGI No. 3 silicone grease — the firmest available.</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>-40 to +200
 no drop pt.</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>3
 transparent
 inorganic thickener / polydimethylsiloxane</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>9,500</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>10ml
 80ml
 500g</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>1,120
 8,950
 37,000</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>On request
 On request
@@ -2295,53 +2311,53 @@
 Silicone Grease</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Silicone grease for low temperatures. Also ideal for plastic-on-plastic and plastic-on-metal lubrication. Excellent oxidation resistance, low oil separation, low evaporation.</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>-70 to +160
 drop pt. +215</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>2
 light brown
 lithium soap / polyphenylmethylsiloxane</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>350,000</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>1,200
 2.6</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>100g
 500g</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>9,390
 31,000</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>On request
 On request
@@ -2357,51 +2373,51 @@
 Silicone Grease</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>The silicone grease with the highest service temperature, for high-temperature, low-speed rotation. Low evaporation even at high temperature.</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>-20 to +290
 no drop pt.</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>2
 black
 special carbon black / polyphenylmethylsiloxane</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>75,000</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>2,100
 1.2</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>30,200</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -2415,51 +2431,51 @@
 Silicone Grease</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Multi-purpose silicone grease for a wide temperature range. Also ideal for plastic-on-plastic and plastic-on-metal lubrication. Excellent oxidation resistance, low oil separation.</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>-40 to +200
 drop pt. +205</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>2
 light brown
 lithium soap / polyphenylmethylsiloxane</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>500,000</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>1,300
 3.3</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>33,000</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
@@ -2473,113 +2489,113 @@
 high adhesion</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Highly adhesive silicone grease with excellent sealing at low speeds. Ideal for lubricating like or unlike materials — metal, plastic, elastomer. Low oil separation even at high temperature.</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>-60 to +180
 drop pt. +210</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>2
 light brown
 lithium soap / polyphenylmethylsiloxane / ester</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>28,000</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>On request</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>*1 Service temperature — the temperature at which the product can be used under continuous conditions; the drop point is higher still, and short-term use up to the drop point is possible.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>*2 NLGI grade (consistency) — centred on No. 2; higher numbers are firmer, lower numbers are softer.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>*3 Mox-Active — a proprietary OKS additive combining organic molybdenum with several solid lubricants. It smooths the lubricated surface and reduces friction and wear.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>*4 Sizes — 400 g items come as cylindrical cartridges (10 per box). A dedicated grease gun (sold separately) is required for use; see the Related Products section.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>*5 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders in units of ten; please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>*6 Dispatch — "On request": please contact us. Dispatch dates are updated according to stock.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>*7 SOS express — items eligible for our emergency delivery service. Request SOS delivery when ordering; service-area restrictions apply. Contact us for details.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>*8 USDA-H1/NSF-H1 — certified by public bodies as lubricants usable where incidental contact with food is possible.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>*9 BIOlogic — the OKS range of biodegradable lubricants built on new technology.</t>
         </is>
@@ -2597,6 +2613,40 @@
     <mergeCell ref="A42:J42"/>
     <mergeCell ref="A41:J41"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2691,49 +2741,49 @@
 German Rail No. 07606</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Double-molybdenum type combining MoS2 with organic molybdenum. Prevents seizure, wear, and stick-slip. For press-fitting parts, lubricating sliding surfaces, running-in, and preventing galling in press forming. Also used for pressing railway wheels onto axles. Resistant to water, oil, chemicals, and hydraulic fluids.</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>black
 MoS2 / organic molybdenum / other solid lubricants / synthetic oil</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>-35 to +450
 (+630)</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>2,400</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>3,460</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>Tube
 *40ml</t>
@@ -2748,49 +2798,49 @@
 Mox-Active</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Double-molybdenum type combining MoS2 with organic molybdenum. Fast acting — no rubbing-in required. The most versatile molybdenum paste. Prevents seizure, wear, and stick-slip under extreme pressure. For press-fitting parts, sliding surfaces, running-in, and preventing galling in press forming. Resistant to water, oil, chemicals, and hydraulic fluids.</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>black
 MoS2 / organic molybdenum / other solid lubricants / synthetic oil</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>-35 to +450
 (+630)</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>9,000</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Tube
 *250g</t>
@@ -2806,49 +2856,49 @@
 spray can</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Double-molybdenum type combining MoS2 with organic molybdenum. Fast acting — no rubbing-in required. The most versatile molybdenum paste. Prevents seizure, wear, and stick-slip under extreme pressure. For press-fitting parts, sliding surfaces, running-in, and preventing galling in press forming. Resistant to water, oil, chemicals, and hydraulic fluids. OKS 220 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>black
 MoS2 / organic molybdenum / other solid lubricants / synthetic oil</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>-35 to +450
 (+630)</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>8,060</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2857,49 +2907,49 @@
 MoS2 High-Temp Paste</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Lubricating paste that forms a dry lubricant film after the base oil evaporates at 180°C; particularly effective from +200 to +450°C. For bearings, sliding surfaces, chains, rollers, and other moving parts in metallurgical plants, hot-forming plants, and drying processes; for kilns, casting ladles, blowers, and other equipment above 200°C. Also ideal for furnace-trolley bearings. Synthetic-oil base, so it does not attack plastics or rubber. Resistant to water, oil, chemicals, and hydraulic fluids. Can be used together with OKS 310.</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>black
 MoS2 / synthetic oil</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>+450
 (+630)</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>3,200</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>11,600</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>Tube</t>
         </is>
@@ -2913,48 +2963,48 @@
 Anti-Seize</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Heavy-metal-free aluminium paste for lubrication and separation. Prevents seizure of bolts on pipe flanges that run hot. Also used for sliding-surface lubrication in chemical and petrochemical plants, ships, offshore, power stations, glassworks, and foundries.</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>metallic silver
 aluminium powder / other solid lubricants / synthetic oil</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>-40 to +1100</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>23,000</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>With brush</t>
         </is>
@@ -2969,54 +3019,54 @@
 MIL-A-907E</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Copper-based anti-seize paste usable up to 1,100°C. Ideal for protecting bolt threads exposed to high temperature around engines and exhaust pipes. Also used on bolts of gas- and oil-fired furnaces.</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>metallic brown
 copper powder / other solid lubricants / synthetic oil</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>+1100</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>2,800</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>8ml
 75ml
 1kg</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>1,700
 4,600
 26,000</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>On request
 On request
 On request</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>Tube
 Tube
@@ -3034,48 +3084,48 @@
 spray can</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Copper-based anti-seize paste usable up to 1,100°C. Ideal for protecting bolt threads exposed to high temperature around exhausts and engines. Also used on bolts of gas- and oil-fired furnaces. OKS 240 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>metallic brown
 copper powder / other solid lubricants / synthetic oil</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>+1100</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>2,800</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>9,550</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -3086,48 +3136,48 @@
 Mox-Active</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Prevents thread corrosion and seizure even after long service. Highly adhesive; corrosion protective. Protects bolt threads exposed to heat and water around the engines and exhaust pipes of off-road motorcycles and vehicles.</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>brown
 copper powder / organic molybdenum / semi-synthetic oil</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>-30 to +1100</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>With brush
 *250ml</t>
@@ -3144,51 +3194,51 @@
 NSF-H2</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>White multi-purpose heat-resistant paste for a wide temperature range. For low-speed, high-load lubrication; also ideal where subject to repeated vibration. Prevents seizure, corrosion, cold fretting, and stick-slip. Prevents seizure of both ferrous and non-ferrous threads; ideal for stainless bolts and for protecting mould and die bolt threads. Also used in refineries, steelworks, cement plants, shipping, offshore, and agricultural machinery. Metal-free formulation with the environment in mind. Corrosion protective; resists seawater, acids, and alkalis. Also suited to cleanliness-critical areas. Strong against vibration, corrosion, and heat, so ideal for preventing disc-brake squeal too. The one product that covers most emergencies on site.</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>white
 white solid lubricants / organic molybdenum / synthetic oil</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>-40 to +1400</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>8ml
 80ml</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>2,030
 4,700</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>On request
 On request</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>Tube
 Tube</t>
@@ -3205,48 +3255,48 @@
 spray can</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>White multi-purpose heat-resistant paste for a wide temperature range. For low-speed, high-load lubrication; also ideal where subject to repeated vibration. Prevents seizure, corrosion, cold fretting, and stick-slip. Prevents seizure of both ferrous and non-ferrous threads; ideal for stainless bolts and for protecting mould and die bolt threads. Also used in refineries, steelworks, cement plants, shipping, offshore, and agricultural machinery. Metal-free formulation with the environment in mind. Corrosion protective; resists seawater, acids, and alkalis. Also suited to cleanliness-critical areas. Strong against vibration, corrosion, and heat, so ideal for preventing disc-brake squeal too. OKS 250 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>white
 white solid lubricants / organic molybdenum / synthetic oil</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>-40 to +1400</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>7,930</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -3257,51 +3307,51 @@
 NSF-H1</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>High-temperature, highly adhesive paste for the food industry. For low-speed, high-load lubrication; also ideal where subject to repeated vibration. Prevents seizure, corrosion, cold fretting, and stick-slip on both ferrous and non-ferrous threads. Metal-free formulation with the environment in mind.</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>light grey
 white solid lubricants / polyglycol / silicate</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>-30 to +1200</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>250g
 200g</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>8,400
 7,500</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>On request
 On request</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>With brush</t>
         </is>
@@ -3314,48 +3364,48 @@
 White Assembly Paste</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>White assembly paste that keeps machinery clean. For paper, packaging, plastic-moulding, textile, and printing machinery and office equipment. Lubrication under vibration or in high humidity. Also highly effective against fretting corrosion. Water resistant.</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>white
 white solid lubricants / lithium grease / white oil</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>-25 to +150</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>0.09</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2,600</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>7,400</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>*250g</t>
         </is>
@@ -3369,48 +3419,48 @@
 high adhesion</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>For lubricating machine-tool chucks. Ideal for lubrication under impact loads and vibration. High-tack formulation that is not washed off by water-soluble cutting fluids.</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>light brown
 white solid lubricants / tackifier / mineral oil</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>-25 to +150</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>0.10</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>3,600</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>15,800</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -3419,55 +3469,55 @@
 White Grease Paste</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>For any machinery under high load where cleanliness and long-term lubrication are required. For precision, paper, textile, and packaging machinery.</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>white
 white solid lubricants / lithium grease / white oil</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>-25 to +125</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>7,300</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>OKS 2771
 High-Load Lubricating Paste
@@ -3475,48 +3525,48 @@
 spray can</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Adhesive white paste with excellent plastic compatibility. For long-term lubrication of heavily loaded parts. Fluoropolymer (PTFE/Teflon*) fortified.</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>white
 PTFE / special ester / additives</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>-20 to +150</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>0.11</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>2,600</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>12,960</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -3525,86 +3575,86 @@
 White High-Temp Paste</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>For hot forming of ferrous and non-ferrous metals: drop forging, hot drawing, hot rolling, hot bending. Small quantities separate and lubricate, extending tool life. Contains no graphite, which would carburise tools or workpieces.</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>white
 white solid lubricants / mineral oil</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>+1150</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>2,400</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>18,900</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr"/>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>*1 Service temperature — the temperature at which the product can be used under continuous conditions. Figures in parentheses apply when contact with air is restricted.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>*2 Weld load — higher values indicate greater load-carrying capacity.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>*3 Mox-Active — a proprietary OKS additive combining organic molybdenum with several solid lubricants. It smooths the lubricated surface and reduces friction and wear.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>*4 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders in units of ten; please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>*5 Dispatch — "On request": please contact us. Dispatch dates are updated according to stock.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>*6 SOS express — items eligible for our emergency delivery service. Request SOS delivery when ordering; service-area restrictions apply. Contact us for details.</t>
         </is>
@@ -3619,6 +3669,23 @@
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A25:J25"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3699,37 +3766,37 @@
 high purity</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Reduces friction and wear over a wide temperature range. Can also be blended into plastics, joints, and seal materials.</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>-185 to +450</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>35,800</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -3739,72 +3806,72 @@
 micro-size</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Reduces friction and wear over a wide temperature range. Particularly suited to lubricating precision-finished surfaces.</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>-185 to +450</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>46,500</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>OKS 510
 MoS2 Bonded Coating
 fast-drying</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Usable over a wider temperature range than OKS 500. Vacuum compatible. Dries at room temperature. Can be recoated.</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>-180 to +450</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>-30</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>OKS 511
 MoS2 Bonded Coating
@@ -3812,32 +3879,32 @@
 spray can</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Usable over a wider temperature range than OKS 500. Vacuum compatible. Dries at room temperature. Can be recoated. OKS 510 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>-180 to +450</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>-30</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>OKS 530
 MoS2 Bonded Coating
@@ -3845,29 +3912,29 @@
 air-drying</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>For low speed, high load, and intermittent operation. Film thickness adjustable by dilution with water.</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>-35 to +450</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>+37</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -3878,132 +3945,132 @@
 air-drying</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>For high temperature and extreme pressure. Graphite dry film; water-dilutable.</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>-35 to +600</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>5kg</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>72,000</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>OKS 570
 PTFE Bonded Coating</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Colourless PTFE coating that keeps lubricated surfaces clean. Forms a lubricating and separating film with anti-stick effect at low speeds and low loads. For all kinds of metal, plastic, ceramic, and wood. Also usable as a release agent for resin moulding.</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>-180 to +260</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>OKS 571
 PTFE Bonded Coating
 spray can</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Colourless PTFE coating that keeps lubricated surfaces clean. Forms a lubricating and separating film with anti-stick effect at low speeds and low loads. For all kinds of metal, plastic, ceramic, and wood. Also usable as a release agent for resin moulding. OKS 570 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>-180 to +260</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>OKS 1300
 Sliding Film
 colourless</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Dry film with UV indicator. Eliminates scatter in screw friction coefficients. Prevents fretting in thread rolling and stainless-screw fabrication. Colourless; for screws of any material. Improves the sliding of glass, ceramics, wood, and metal. Proven for lubricating shutters, blinds, and sunshades.</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>-60 to +100</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>+68</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -4014,32 +4081,32 @@
 spray can</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Dry film. Eliminates scatter in screw friction coefficients. Prevents fretting in thread rolling and stainless-screw fabrication. Colourless; for screws of any material. Improves the sliding of glass, ceramics, wood, and metal. Proven for lubricating shutters, blinds, and sunshades. OKS 1300 filled into a spray can; without the UV indicator.</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>-60 to +100</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>+68</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>OKS 1710
 Sliding Film
@@ -4047,32 +4114,32 @@
 water-based concentrate</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Dry-film lubricant with UV indicator. Prevents cold welding. Ideal for friction control on assembly lines using galvanised or stainless screws. Dilutable with water up to 1:5 to suit the required friction coefficient (standard dilution 1:2). After drying, an anti-corrosion additive prevents rust. The water-soluble components are biodegradable; the non-soluble components are environmentally harmless.</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>+60</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>OKS 1750
 Sliding Film
@@ -4080,32 +4147,32 @@
 water-based concentrate</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Dry-film lubricant with UV indicator. Non-tacky. Prevents cold welding of austenitic steels. Ideal for friction control on assembly lines using galvanised screws, e.g. for chipboard. Dilutable with water up to 1:5 to suit the required friction coefficient (standard dilution 1:2). An anti-corrosion additive prevents rust.</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>+70</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>OKS 1765
 Sliding Film
@@ -4113,53 +4180,53 @@
 water-based concentrate</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Dry-film lubricant with UV indicator. Non-tacky. For pre-coating before thread rolling. Dilutable with water up to 1:5 to suit the required friction coefficient (standard dilution 1:2).</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>+70</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>*1 Service temperature — the temperature at which the product can be used under continuous conditions.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>*2 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders in units of ten; please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>*3 Dispatch — "On request": please contact us. Dispatch dates are updated according to stock.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>*4 SOS express — items eligible for our emergency delivery service. Request SOS delivery when ordering; service-area restrictions apply. Contact us for details.</t>
         </is>
@@ -4172,6 +4239,12 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4253,37 +4326,37 @@
 Mox-Active*2</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>MoS2 additive for blending into standard industrial oils. Reduces friction, temperature, wear, and noise; smooths and conditions metal surfaces; maintains lubrication even if the oil film fails. Does not settle out; passes through filters without clogging; unaffected by magnetic filters.</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Temperature range of the oil it is added to</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>87,000</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -4294,37 +4367,37 @@
 Mox-Active*2</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>For emergency lubrication when temperatures rise above normal or oiling intervals are extended.</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>-30 to +250</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>60,000</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -4335,37 +4408,37 @@
 Mox-Active*2</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Keeps machinery clean. Low evaporation; no residue after evaporation. Drip resistant. Steam resistant.</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>-40 to +250</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>60,000</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -4377,90 +4450,90 @@
 spray can</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Keeps machinery clean. Low evaporation; no residue after evaporation. Drip resistant. Steam resistant. OKS 352 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>-40 to +250</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>7,650</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>OKS 360
 High-Performance
 Corrosion Protection Oil</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Adhesive anti-rust and anti-corrosion oil for harsh climatic conditions. Excellent lubricity. For indoor and outdoor use.</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>-40 to +80</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>5L
 25L</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>59,500
 262,500</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>OKS 361
 High-Performance
@@ -4468,37 +4541,37 @@
 spray can</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Adhesive anti-rust and anti-corrosion oil for harsh climatic conditions. Excellent lubricity. For indoor and outdoor use. OKS 360 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>-40 to +80</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>9,070</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -4510,37 +4583,37 @@
 spray can</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>High-performance lubricating oil with strong penetration. Colourless, tasteless, odourless.</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>-10 to +180</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>6,300</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -4551,39 +4624,39 @@
 NSF-H1*6</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Excellent wear resistance. Long life thanks to high-temperature stability and oxidation resistance. Tasteless, odourless. Chemically resistant — withstands steam, alkalis, acids, and other sterilising and cleaning agents.</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>0 to +160</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>5L
 25L</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>46,000
 202,000</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -4594,39 +4667,39 @@
 NSF-H1*6</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Excellent wear resistance. Long life thanks to high-temperature stability and oxidation resistance. Tasteless, odourless. Chemically resistant — withstands steam, alkalis, acids, and other sterilising and cleaning agents.</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>0 to +160</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>460</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>5L
 25L</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>50,000
 222,000</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -4639,37 +4712,37 @@
 spray can</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Tasteless, odourless. Highly adhesive with excellent load-carrying capacity. Fluoropolymer (PTFE/Teflon*) fortified. Chemically resistant — withstands steam, alkalis, acids, and other sterilising and cleaning agents. PAO based.</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>-35 to +135</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>7,000</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
@@ -4684,39 +4757,39 @@
 NSF-H1*6</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Versatile long-term lubricant with excellent lubricity and strong adhesion. Tasteless, odourless.</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>-10 to +180</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>5L
 25L</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>53,000
 240,000</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -4727,39 +4800,39 @@
 NSF-H1*6</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Long life. Excellent wear resistance. Tasteless, odourless.</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>-15 to +200</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>5L
 25L</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>44,850
 201,750</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -4771,37 +4844,37 @@
 NSF-H1*6</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Tasteless, odourless emulsion. Wear resistant and corrosion protective. Excellent lubricity — and dissolves and washes away sugar at the same time.</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>0 to +80</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>46,000</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -4812,37 +4885,37 @@
 Mox-Active*2</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Cutting oil for machining a wide range of metals. Free of chlorine and phosphorus, so there is no strong odour and little impact on people or the environment.</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>250ml</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>2,750</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -4854,37 +4927,37 @@
 spray can</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Cutting oil for machining a wide range of metals. Free of chlorine and phosphorus, so there is no strong odour and little impact on people or the environment. OKS 390 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>5,470</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -4893,37 +4966,37 @@
 Multi Oil</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Multi-purpose lubricant: rust removal, screw loosening, moisture displacement, lubrication, cleaning, restoring electrical contacts, and rust protection.</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>-30 to +60</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>17,250</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -4933,37 +5006,37 @@
 spray can</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Multi-purpose lubricant: rust removal, screw loosening, moisture displacement, lubrication, cleaning, restoring electrical contacts, and rust protection. OKS 600 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>-30 to +60</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>300ml</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>2,300</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
@@ -4978,37 +5051,37 @@
 Mox-Active*2</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>All-round lubricant that keeps machinery clean. Strong penetration reaches the finest clearances. Excellent extreme-pressure performance from white solid lubricants. Also ideal for lubricating machinery without central lubrication.</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>-30 to +80</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>26,250</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr"/>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -5020,37 +5093,37 @@
 spray can</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>All-round lubricant that keeps machinery clean. Strong penetration reaches the finest clearances. Excellent extreme-pressure performance from white solid lubricants. Also ideal for lubricating machinery without central lubrication. OKS 670 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>-30 to +80</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>300ml</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>3,870</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
@@ -5063,37 +5136,37 @@
 Synthetic Oil</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Synthetic oil for cleaning, lubrication, and rust protection. A transparent protective film guards metal surfaces.</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>-50 to +100</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>39,000</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr"/>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -5103,82 +5176,82 @@
 non-gas spray container</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Synthetic oil for cleaning, lubrication, and rust protection. A transparent protective film guards metal surfaces. OKS 700 filled into a non-gas pump-spray container.</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>-50 to +100</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>100ml</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>2,600</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>*1 Service temperature — the temperature at which the product can be used under continuous conditions.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>*2 Mox-Active — a proprietary OKS additive combining organic molybdenum with several solid lubricants. It smooths the lubricated surface and reduces friction and wear.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>*3 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders in units of ten; please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>*4 Dispatch — "On request": please contact us. Dispatch dates are updated according to stock.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>*5 SOS express — items eligible for our emergency delivery service. Request SOS delivery when ordering; service-area restrictions apply. Contact us for details.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>*6 USDA-H1/NSF-H1 — certified by public bodies as lubricants usable where incidental contact with food is possible.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>*7 BIOlogic — the OKS range of biodegradable lubricants built on new technology.</t>
         </is>
@@ -5194,6 +5267,27 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:H31"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5275,37 +5369,37 @@
 MIL-C-16173 grade 1</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Non-tacky rust preventive usable under all climatic conditions. Unlike ordinary lubricating oils, the protective film does not need to be removed before operation. US military specification item, used where equipment and fittings at sea need maximum protection from salt water.</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>-40 to +70</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>640</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>27,000</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -5317,37 +5411,37 @@
 MIL-C-16173 grade 1</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Non-tacky rust preventive usable under all climatic conditions. Unlike ordinary lubricating oils, the protective film does not need to be removed before operation. US military specification item, used where equipment and fittings at sea need maximum protection from salt water. OKS 2100 filled into a spray container.</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>-40 to +70</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>640</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>4,690</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
@@ -5362,40 +5456,40 @@
 spray can</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Highly water-repellent, non-tacky rust preventive for moulds and dies. Green colour makes it easy to confirm a uniform coating.</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>-40 to +70</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>›1000</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>5,020</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>OKS 2511
 Zinc Coating
@@ -5403,211 +5497,211 @@
 TÜV certified</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>For heavy-duty corrosion protection; passes the DIN 53167 salt spray test. Heat resistant to +490°C. Spot-weldable. For steel structures, bridges, ships, offshore structures, plant, and vehicles. Also ideal for repairing axle undercoating and as a primer before painting. Dries in 5 minutes at room temperature; a scratch-resistant protective film forms in 2 hours; paintable after 6 hours. The aerosol can uses a self-cleaning valve to prevent clogging.</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>+490</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>6,300</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>OKS 2521
 Gloss Zinc
 spray can</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Drying rust preventive with a bright metallic finish. Weldable and paintable. Protects against scratches. Same drying times as OKS 2511.</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>+490</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>6,650</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>OKS 2531
 Alu-Metallic</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Drying rust preventive with a matt aluminium finish. Usable on all metals. Electrically conductive. Ideal for maintaining hot pipework and flues; also used on car exhaust pipes. Same drying times as OKS 2511.</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>-70 to +800</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>5,950</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>OKS 2541
 Stainless Steel
 spray can</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Rust preventive for stainless steel in high-humidity environments. Contains stainless steel powder. Resists impact and peeling.</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>to +100</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>7,250</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>OKS 360
 High-Performance
 Corrosion Protection Oil</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>For rust protection under severe conditions. Adhesive. Usable indoors and outdoors. Also ideal for export packing of machinery and parts.</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>-40 to +80</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Transferred</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>OKS 361
 High-Performance
@@ -5615,37 +5709,37 @@
 spray can</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>For rust protection under severe conditions. Adhesive. Usable indoors and outdoors. Also ideal for export packing of machinery and parts. OKS 360 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>-40 to +80</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>9,070</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -5656,41 +5750,41 @@
 NATO spec. G-460</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Special grease with outstanding corrosion protection even under water. Proven in humid workplaces and coastal areas.</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>-25 to +80
 drop pt. +115</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>›700</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>400ml
 1kg</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>5,850
 9,500</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>On request
 On request</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
@@ -5703,37 +5797,37 @@
 Multi Oil</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Short-term rust protection combined with lubrication. A maintenance essential with countless uses.</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>-30 to +60</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>17,250</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -5743,37 +5837,37 @@
 spray can</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Short-term rust protection combined with lubrication. A maintenance essential with countless uses. OKS 600 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>-30 to +60</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
@@ -5786,37 +5880,37 @@
 Synthetic Oil</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Long-lasting rust protection from a thin film. Economical — a small amount protects a large area. For precision equipment such as measuring instruments.</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>-50 to +100</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>39,000</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -5826,68 +5920,68 @@
 non-gas spray container</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Long-lasting rust protection from a thin film. Economical — a small amount protects a large area. OKS 700 filled into a non-gas spray container. For precision equipment such as measuring instruments.</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>-50 to +100</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>100ml</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>2,600</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>*1 Service temperature — the temperature at which the product can be used under continuous conditions; the drop point is higher still, and short-term use up to the drop point is possible.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>*2 Sizes — 400 g items come as cylindrical cartridges (10 per box). A dedicated grease gun is required for use; sold separately at 10,000 JPY.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>*3 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders in units of ten; please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>*4 Dispatch — "On request": please contact us. Dispatch dates are updated according to stock.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>*5 SOS express — items eligible for our emergency delivery service. Request SOS delivery when ordering; service-area restrictions apply. Contact us for details.</t>
         </is>
@@ -5901,6 +5995,16 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A22:H22"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5982,37 +6086,37 @@
 spray can</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Powerful penetration. Contains MoS2. Removes rust from metal surfaces and frees seized screws. Water repellent. Short-term rust protection.</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>-30 to +50</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>grey</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -6021,38 +6125,38 @@
 Heat-Sink Paste</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Heat-dissipating paste that protects electronic components — CPUs, sensors, probes, diodes, transistors, thyristors — from heat. High thermal conductivity. Does not attack materials.</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>-40 to +200
 no drop pt.</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>white</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>40ml</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>40ml</t>
         </is>
@@ -6066,37 +6170,37 @@
 Release Agent</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Highly effective release lubricant with an antistatic additive. Chemically neutral. Solvent-free.</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>-60 to +200</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>colourless</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>59,000</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -6108,37 +6212,37 @@
 spray can</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Highly effective release lubricant with an antistatic additive. Chemically neutral. Solvent-free. OKS 1360 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>-60 to +200</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>colourless</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>3,720</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Spray can
 *400ml</t>
@@ -6154,33 +6258,33 @@
 spray can</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Makes painting, printing, bonding, and plating of moulded plastic surfaces easier. Non-tacky. Silicone-free.</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>colourless</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>2,550</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Spray can
 *400ml</t>
@@ -6196,33 +6300,33 @@
 concentrate</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Prevents weld spatter from sticking to workpieces and welding nozzles. Dilute with water for use.</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>colourless</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>26,000</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -6234,33 +6338,33 @@
 spray can</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Prevents weld spatter from sticking to workpieces and welding nozzles. OKS 1600 filled into a spray can. Water-dilutable type.</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>colourless</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>2,560</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Spray can
 *400ml</t>
@@ -6275,33 +6379,33 @@
 spray can</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Powerful degreaser. Quickly removes grease, oil, and other soiling. Fast drying — evaporates rapidly without residue. VCI additive provides short-term rust protection. OKS 2610 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr"/>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>colourless</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Spray can</t>
         </is>
@@ -6315,33 +6419,33 @@
 spray can</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Electrical contact cleaner that quickly penetrates and cleans the finest gaps. Removes dirt and oxides without dripping. Restores contacts; prevents stray currents. CFC-free!</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>colourless</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>9,500</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -6350,37 +6454,37 @@
 Leak Detector</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Foam instantly reveals even the slightest gas leak.</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>+80</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>colourless</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>11,950</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -6390,37 +6494,37 @@
 spray can</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Foam instantly reveals even the slightest gas leak. OKS 2800 filled into a spray can.</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>+80</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>colourless</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>2,230</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -6430,33 +6534,33 @@
 spray can</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Blows dust and debris off electronic components and precision equipment. Oil-free, dry-air type. CFC-free!</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr"/>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>colourless</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Spray can</t>
         </is>
@@ -6470,79 +6574,79 @@
 spray can</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Increases belt tension by 50% and improves power transmission. Highly adhesive; prevents slip. Keeps belts from drying out, extending their life. Usable on V-belts, round belts, flat belts, and many other belt types.</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>+80</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>colourless</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>5,670</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Spray can</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>*1 Service temperature — the temperature at which the product can be used under continuous conditions. Figures in parentheses apply when contact with air is restricted.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>*2 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders in units of ten; please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>*3 Dispatch — "On request": please contact us. Dispatch dates are updated according to stock.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>*4 SOS express — items eligible for our emergency delivery service. Request SOS delivery when ordering; service-area restrictions apply. Contact us for details.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>*5 USDA-H1/NSF-H1 — certified by public bodies as lubricants usable where incidental contact with food is possible.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>*6 BIOlogic — the OKS range of biodegradable lubricants built on new technology.</t>
         </is>
@@ -6557,6 +6661,21 @@
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6624,96 +6743,96 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2118</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>High-Pressure Grease Gun
 LS-600E</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>For 400 g cartridge greases</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Same day</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Lever type, with grip.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Grease Nipples*3</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Types A, B, C; pin type; button head</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Inch &amp; metric</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Quote</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>On request</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>On request</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>JIS and overseas standards in all sizes. Dust caps sold separately.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>*1 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders of ten or more; please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>*2 Dispatch — "On request": please contact us. Dispatch dates are updated according to stock.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>*3 Grease nipples — please specify the thread standard and material when ordering. Contact us for details.</t>
         </is>

--- a/public/downloads/factory-express-catalogue-en.xlsx
+++ b/public/downloads/factory-express-catalogue-en.xlsx
@@ -522,14 +522,14 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Issued: 2026-07-18</t>
+          <t>Issued: 2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>The E-price is the unit price (JPY) for an order of one; discounted pricing applies to orders in units of ten. Prices and lead times are subject to change without notice.</t>
+          <t>The E-price is the unit price (JPY) for an order of one. Prices and lead times are subject to change without notice.</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>*5 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders in units of ten; please enquire using the fax quote request form.</t>
+          <t>*5 E-price — the price for an order quantity of one (JPY). Please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>*4 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders in units of ten; please enquire using the fax quote request form.</t>
+          <t>*4 E-price — the price for an order quantity of one (JPY). Please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>*2 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders in units of ten; please enquire using the fax quote request form.</t>
+          <t>*2 E-price — the price for an order quantity of one (JPY). Please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>*3 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders in units of ten; please enquire using the fax quote request form.</t>
+          <t>*3 E-price — the price for an order quantity of one (JPY). Please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>
@@ -5962,14 +5962,14 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>*2 Sizes — 400 g items come as cylindrical cartridges (10 per box). A dedicated grease gun is required for use; sold separately at 10,000 JPY.</t>
+          <t>*2 Sizes — 400 g items come as cylindrical cartridges (10 per box). A dedicated grease gun is required for use.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>*3 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders in units of ten; please enquire using the fax quote request form.</t>
+          <t>*3 E-price — the price for an order quantity of one (JPY). Please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>*2 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders in units of ten; please enquire using the fax quote request form.</t>
+          <t>*2 E-price — the price for an order quantity of one (JPY). Please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>
@@ -6745,7 +6745,7 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>5,800</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
@@ -6820,7 +6820,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>*1 E-price — the price for an order quantity of one (JPY). Discounted prices apply to orders of ten or more; please enquire using the fax quote request form.</t>
+          <t>*1 E-price — the price for an order quantity of one (JPY). Please enquire using the fax quote request form.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/factory-express-catalogue-en.xlsx
+++ b/public/downloads/factory-express-catalogue-en.xlsx
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>TEL +81-72-284-1711 / FAX +81-72-298-7790 / oilkey@oilkey.co.jp</t>
+          <t>TEL +81-72-284-1711 / FAX +81-72-298-7790</t>
         </is>
       </c>
     </row>
